--- a/processed_ruby_restored_xlsx/sc032c_３日目：凛.ss.xlsx
+++ b/processed_ruby_restored_xlsx/sc032c_３日目：凛.ss.xlsx
@@ -717,8 +717,8 @@
       <c r="B17" s="1" t="inlineStr">
         <is>
           <t>The islanders wouldn't steal the bus, and even if it
-was taken, there's nowhere to go, so they don't bother
-with security.</t>
+was taken, there's nowhere to go, so they don't
+bother with security.</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -748,8 +748,8 @@
       </c>
       <c r="B19" s="1" t="inlineStr">
         <is>
-          <t>Still... Comic RO is on my mind too, but for now, I'll
-go check it out.</t>
+          <t>Still... Comic RO is on my mind too, but for now,
+I'll go check it out.</t>
         </is>
       </c>
       <c r="C19" t="n">
@@ -872,8 +872,8 @@
       </c>
       <c r="B27" s="1" t="inlineStr">
         <is>
-          <t>Hardly much for self-defense, but I grabbed a shoehorn
-and left the dorm.</t>
+          <t>Hardly much for self-defense, but I grabbed a
+shoehorn and left the dorm.</t>
         </is>
       </c>
       <c r="C27" t="n">
@@ -1073,8 +1073,8 @@
       </c>
       <c r="B40" s="1" t="inlineStr">
         <is>
-          <t>There was no sign of anyone there, so I quietly opened
-the door and slipped inside...</t>
+          <t>There was no sign of anyone there, so I quietly
+opened the door and slipped inside...</t>
         </is>
       </c>
       <c r="C40" t="n">
@@ -1227,7 +1227,8 @@
       </c>
       <c r="B50" s="1" t="inlineStr">
         <is>
-          <t>But a contented-sounding sigh escapes her sealed lips.</t>
+          <t>But a contented-sounding sigh escapes her sealed
+lips.</t>
         </is>
       </c>
       <c r="C50" t="n">
@@ -1908,8 +1909,9 @@
       </c>
       <c r="B94" s="1" t="inlineStr">
         <is>
-          <t>When I have naughty thoughts, she’s the first to tease
-me about it, and she can be a bit precocious too.</t>
+          <t>When I have naughty thoughts, she’s the first to
+tease me about it, and she can be a bit precocious
+too.</t>
         </is>
       </c>
       <c r="C94" t="n">
@@ -2031,8 +2033,8 @@
       </c>
       <c r="B102" s="1" t="inlineStr">
         <is>
-          <t>But the bus's vibration must be nicely stimulating the
-soft flesh between her legs.</t>
+          <t>But the bus's vibration must be nicely stimulating
+the soft flesh between her legs.</t>
         </is>
       </c>
       <c r="C102" t="n">
@@ -2079,8 +2081,8 @@
       </c>
       <c r="B105" s="1" t="inlineStr">
         <is>
-          <t>...I replayed the time before I came here and the time
-after I arrived.</t>
+          <t>...I replayed the time before I came here and the
+time after I arrived.</t>
         </is>
       </c>
       <c r="C105" t="n">
@@ -2252,7 +2254,8 @@
       </c>
       <c r="B116" s="1" t="inlineStr">
         <is>
-          <t>「Ugh, haa... ah, mm... fuu, fuu... uuh... nn, nnn...！」</t>
+          <t>「Ugh, haa... ah, mm... fuu, fuu... uuh... nn,
+nnn...！」</t>
         </is>
       </c>
       <c r="C116" t="n">
@@ -2267,8 +2270,8 @@
       </c>
       <c r="B117" s="1" t="inlineStr">
         <is>
-          <t>Rin-chan, not realizing I'm nearby, gets worked up all
-on her own.</t>
+          <t>Rin-chan, not realizing I'm nearby, gets worked up
+all on her own.</t>
         </is>
       </c>
       <c r="C117" t="n">
@@ -2330,7 +2333,8 @@
       </c>
       <c r="B121" s="1" t="inlineStr">
         <is>
-          <t>You must never do anything that would make a girl sad！</t>
+          <t>You must never do anything that would make a girl
+sad！</t>
         </is>
       </c>
       <c r="C121" t="n">
@@ -2451,8 +2455,8 @@
       </c>
       <c r="B129" s="1" t="inlineStr">
         <is>
-          <t>I force myself to stifle my ragged breathing as best I
-can...</t>
+          <t>I force myself to stifle my ragged breathing as best
+I can...</t>
         </is>
       </c>
       <c r="C129" t="n">
@@ -2512,8 +2516,8 @@
       </c>
       <c r="B133" s="1" t="inlineStr">
         <is>
-          <t>I don't even know how to put it—I really don't want to
-think about it.</t>
+          <t>I don't even know how to put it—I really don't want
+to think about it.</t>
         </is>
       </c>
       <c r="C133" t="n">
@@ -2604,8 +2608,8 @@
       </c>
       <c r="B139" s="1" t="inlineStr">
         <is>
-          <t>Then, she gently let go of the shift lever between her
-legs...</t>
+          <t>Then, she gently let go of the shift lever between
+her legs...</t>
         </is>
       </c>
       <c r="C139" t="n">

--- a/processed_ruby_restored_xlsx/sc032c_３日目：凛.ss.xlsx
+++ b/processed_ruby_restored_xlsx/sc032c_３日目：凛.ss.xlsx
@@ -484,7 +484,7 @@
       </c>
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>Rin-chan... maybe.</t>
+          <t>Maybe it's Rin-chan.</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -499,8 +499,8 @@
       </c>
       <c r="B3" s="1" t="inlineStr">
         <is>
-          <t>She's shy, but I think the one she's actually most
-aware of is Rin-chan.</t>
+          <t>She's shy, but I think she's actually most conscious
+of Rin-chan.</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -515,9 +515,9 @@
       </c>
       <c r="B4" s="1" t="inlineStr">
         <is>
-          <t>Up until now she'd been vaguely responding to naughty
-stuff, but what if reading that book made her clearly
-start to notice it...？</t>
+          <t>Up until now she'd only reacted vaguely to sexual
+things, but what if, after reading that book, she
+began to become clearly aware of them...?</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -563,8 +563,7 @@
       </c>
       <c r="B7" s="1" t="inlineStr">
         <is>
-          <t>After all, she doesn't say much, but she's
-sharp-tongued.</t>
+          <t>She doesn't say much, but she's quick-witted.</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -594,7 +593,7 @@
       </c>
       <c r="B9" s="1" t="inlineStr">
         <is>
-          <t>...Anyway, I should go look for Rin-chan.</t>
+          <t>...Anyway, I'll go look for Rin-chan.</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -609,8 +608,7 @@
       </c>
       <c r="B10" s="1" t="inlineStr">
         <is>
-          <t>It was when I stepped out into the hallway thinking
-that.</t>
+          <t>That's when I stepped out into the hallway.</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -640,7 +638,7 @@
       </c>
       <c r="B12" s="1" t="inlineStr">
         <is>
-          <t>From afar, I heard a sound I knew well.</t>
+          <t>In the distance, I heard a familiar sound.</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -671,7 +669,8 @@
       </c>
       <c r="B14" s="1" t="inlineStr">
         <is>
-          <t>Because that sound was the bus's engine.</t>
+          <t>Because what I just heard was the sound of a bus
+engine.</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -701,7 +700,7 @@
       </c>
       <c r="B16" s="1" t="inlineStr">
         <is>
-          <t>The keys are always left in.</t>
+          <t>The key is always left in the ignition.</t>
         </is>
       </c>
       <c r="C16" t="n">
@@ -717,7 +716,7 @@
       <c r="B17" s="1" t="inlineStr">
         <is>
           <t>The islanders wouldn't steal the bus, and even if it
-was taken, there's nowhere to go, so they don't
+were stolen, there's nowhere to go, so they don't
 bother with security.</t>
         </is>
       </c>
@@ -748,8 +747,8 @@
       </c>
       <c r="B19" s="1" t="inlineStr">
         <is>
-          <t>Still... Comic RO is on my mind too, but for now,
-I'll go check it out.</t>
+          <t>But... I'm curious about Comic RO too. For now, I'll
+go take a look.</t>
         </is>
       </c>
       <c r="C19" t="n">
@@ -796,7 +795,7 @@
       </c>
       <c r="B22" s="1" t="inlineStr">
         <is>
-          <t>...But why is the engine running？</t>
+          <t>...But why is the engine running?</t>
         </is>
       </c>
       <c r="C22" t="n">
@@ -826,7 +825,7 @@
       </c>
       <c r="B24" s="1" t="inlineStr">
         <is>
-          <t>A bus came to life？！</t>
+          <t>Was the bus possessed?!</t>
         </is>
       </c>
       <c r="C24" t="n">
@@ -856,8 +855,8 @@
       </c>
       <c r="B26" s="1" t="inlineStr">
         <is>
-          <t>I don't know what might come out, but anyway, I have
-no choice but to go and see...！</t>
+          <t>I don't know what might come out, but I have no
+choice — I have to go see for myself...!</t>
         </is>
       </c>
       <c r="C26" t="n">
@@ -872,8 +871,8 @@
       </c>
       <c r="B27" s="1" t="inlineStr">
         <is>
-          <t>Hardly much for self-defense, but I grabbed a
-shoehorn and left the dorm.</t>
+          <t>It was hardly adequate for self-defense, but I
+grabbed a shoehorn and left the dorm.</t>
         </is>
       </c>
       <c r="C27" t="n">
@@ -920,9 +919,9 @@
       </c>
       <c r="B30" s="1" t="inlineStr">
         <is>
-          <t>…As I got closer to the garage where the buses are
-kept, the night's cold air carried the engine's
-vibration sounds to me.</t>
+          <t>…As I approached the garage where the buses were
+parked, the cold night air carried the engine's
+rumble.</t>
         </is>
       </c>
       <c r="C30" t="n">
@@ -998,7 +997,7 @@
       </c>
       <c r="B35" s="1" t="inlineStr">
         <is>
-          <t>...What should I do？</t>
+          <t>...What should I do?</t>
         </is>
       </c>
       <c r="C35" t="n">
@@ -1043,7 +1042,7 @@
       </c>
       <c r="B38" s="1" t="inlineStr">
         <is>
-          <t>I'm scared, so let's wait and see.</t>
+          <t>I'm scared, so I'll wait and see.</t>
         </is>
       </c>
       <c r="C38" t="n">
@@ -1058,7 +1057,7 @@
       </c>
       <c r="B39" s="1" t="inlineStr">
         <is>
-          <t>I decided that and grabbed the driver's-side door.</t>
+          <t>I made up my mind and grabbed the driver's side door.</t>
         </is>
       </c>
       <c r="C39" t="n">
@@ -1165,8 +1164,8 @@
       </c>
       <c r="B46" s="1" t="inlineStr">
         <is>
-          <t>No—she's pressing her between (my/her) legs against
-the gear shift... I get that. I get it, but...</t>
+          <t>No—she's pressing her crotch against the gear
+shift... I can see that. I get it, but...</t>
         </is>
       </c>
       <c r="C46" t="n">
@@ -1196,7 +1195,7 @@
       </c>
       <c r="B48" s="1" t="inlineStr">
         <is>
-          <t>「…nngh, nnh…ngh…」</t>
+          <t>「…nngh…nnh…ngh…」</t>
         </is>
       </c>
       <c r="C48" t="n">
@@ -1227,8 +1226,7 @@
       </c>
       <c r="B50" s="1" t="inlineStr">
         <is>
-          <t>But a contented-sounding sigh escapes her sealed
-lips.</t>
+          <t>But a contented sigh escapes her pressed lips.</t>
         </is>
       </c>
       <c r="C50" t="n">
@@ -1243,9 +1241,9 @@
       </c>
       <c r="B51" s="1" t="inlineStr">
         <is>
-          <t>The position pressing between her legs, and this
-somehow mismatched expression, point to only one
-conclusion.</t>
+          <t>The fact that she's pressing something between her
+legs, together with that oddly incongruous
+expression, points to only one conclusion.</t>
         </is>
       </c>
       <c r="C51" t="n">
@@ -1291,7 +1289,7 @@
       </c>
       <c r="B54" s="1" t="inlineStr">
         <is>
-          <t>「…! …! Nn… nn…」</t>
+          <t>「…nngh…nnh…」</t>
         </is>
       </c>
       <c r="C54" t="n">
@@ -1306,7 +1304,8 @@
       </c>
       <c r="B55" s="1" t="inlineStr">
         <is>
-          <t>Rin-chan's breath gets lost in the hum of the engine.</t>
+          <t>Rin-chan's sigh is drowned out by the rumble of the
+engine.</t>
         </is>
       </c>
       <c r="C55" t="n">
@@ -1321,7 +1320,7 @@
       </c>
       <c r="B56" s="1" t="inlineStr">
         <is>
-          <t>Still, I can feel something like a sultry sheen.</t>
+          <t>Even so, I can sense a kind of sensuality.</t>
         </is>
       </c>
       <c r="C56" t="n">
@@ -1368,8 +1367,8 @@
       </c>
       <c r="B59" s="1" t="inlineStr">
         <is>
-          <t>Rin-chan must have had feelings about the bus's
-vibration for a while.</t>
+          <t>Rin-chan must have had some thoughts about the bus's
+vibrations for some time.</t>
         </is>
       </c>
       <c r="C59" t="n">
@@ -1384,7 +1383,7 @@
       </c>
       <c r="B60" s="1" t="inlineStr">
         <is>
-          <t>And she was interested in naughty things too.</t>
+          <t>And Rin-chan was also interested in erotic things.</t>
         </is>
       </c>
       <c r="C60" t="n">
@@ -1399,7 +1398,7 @@
       </c>
       <c r="B61" s="1" t="inlineStr">
         <is>
-          <t>Now that it’s come to this, her shy personality makes
+          <t>In a situation like this, Rin-chan's shyness makes
 her act distant…</t>
         </is>
       </c>
@@ -1430,7 +1429,7 @@
       </c>
       <c r="B63" s="1" t="inlineStr">
         <is>
-          <t>「Nn… fuuh… nn… nn…」</t>
+          <t>「…nngh… fuu… nnh… nnh…」</t>
         </is>
       </c>
       <c r="C63" t="n">
@@ -1461,9 +1460,9 @@
       </c>
       <c r="B65" s="1" t="inlineStr">
         <is>
-          <t>I’d been wondering about this for a while, but I
-couldn’t press my between-her-legs against her with
-everyone around.</t>
+          <t>Rin-chan had been wondering about trying this for a
+while, but she couldn’t press her crotch against the
+shift lever with everyone around.</t>
         </is>
       </c>
       <c r="C65" t="n">
@@ -1494,7 +1493,8 @@
       </c>
       <c r="B67" s="1" t="inlineStr">
         <is>
-          <t>…If that’s the case, how unbearably cute she is.</t>
+          <t>…If that's the case, how touchingly adorable Rin-chan
+is.</t>
         </is>
       </c>
       <c r="C67" t="n">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="B69" s="1" t="inlineStr">
         <is>
-          <t>「Fuh… nn, nnn… fuuh, nn… nn…」</t>
+          <t>「…fuh… nnh… nnh… fuu… nnh… nnh…」</t>
         </is>
       </c>
       <c r="C69" t="n">
@@ -1554,9 +1554,8 @@
       </c>
       <c r="B71" s="1" t="inlineStr">
         <is>
-          <t>Even though she still thinks she's the only one here,
-that childishly embarrassed feeling makes my chest
-ache.</t>
+          <t>Even though she thinks she's the only one here, her
+childlike embarrassment still pierces my chest.</t>
         </is>
       </c>
       <c r="C71" t="n">
@@ -1571,9 +1570,9 @@
       </c>
       <c r="B72" s="1" t="inlineStr">
         <is>
-          <t>...I've been holding back until now, but maybe after
-reading naughty books with everyone, my urges just
-couldn't be held in anymore.</t>
+          <t>Rin-chan had been holding back until now, but maybe
+after reading erotic books with everyone, she
+couldn't suppress her urges anymore.</t>
         </is>
       </c>
       <c r="C72" t="n">
@@ -1588,8 +1587,8 @@
       </c>
       <c r="B73" s="1" t="inlineStr">
         <is>
-          <t>If that's the case, I think she should do it as much
-as she wants.</t>
+          <t>If that's the case, she should do it to her heart's
+content.</t>
         </is>
       </c>
       <c r="C73" t="n">
@@ -1604,7 +1603,7 @@
       </c>
       <c r="B74" s="1" t="inlineStr">
         <is>
-          <t>Still, that's pretty bold of her.</t>
+          <t>Still, that's pretty bold of Rin-chan.</t>
         </is>
       </c>
       <c r="C74" t="n">
@@ -1634,7 +1633,7 @@
       </c>
       <c r="B76" s="1" t="inlineStr">
         <is>
-          <t>「Huff... nn, nngh... nnh...」</t>
+          <t>「…fuu… nn… nngh… nnh…」</t>
         </is>
       </c>
       <c r="C76" t="n">
@@ -1695,7 +1694,7 @@
       </c>
       <c r="B80" s="1" t="inlineStr">
         <is>
-          <t>For Rin-chan's sake, she can't be found out.</t>
+          <t>For Rin-chan's sake, we mustn't get caught.</t>
         </is>
       </c>
       <c r="C80" t="n">
@@ -1710,7 +1709,7 @@
       </c>
       <c r="B81" s="1" t="inlineStr">
         <is>
-          <t>Right now... her awkward eyes were saying that.</t>
+          <t>Just now... Rin-chan's embarrassed eyes said as much.</t>
         </is>
       </c>
       <c r="C81" t="n">
@@ -1756,8 +1755,9 @@
       </c>
       <c r="B84" s="1" t="inlineStr">
         <is>
-          <t>From past experience, you know that even if you start
-the bus's engine, it won't be heard inside the dorm.</t>
+          <t>From past experience, Rin-chan would probably know
+that even if she started the bus's engine, it
+wouldn't be heard inside the dorm.</t>
         </is>
       </c>
       <c r="C84" t="n">
@@ -1772,8 +1772,8 @@
       </c>
       <c r="B85" s="1" t="inlineStr">
         <is>
-          <t>Still, you can't help being conscious of it because
-you feel guilty.</t>
+          <t>Still, the reason I can't help being aware of it is
+that I feel guilty.</t>
         </is>
       </c>
       <c r="C85" t="n">
@@ -1803,7 +1803,7 @@
       </c>
       <c r="B87" s="1" t="inlineStr">
         <is>
-          <t>「Ah... uh, uuuu... fu, uuu........」</t>
+          <t>「Ah... uh... uuu... fuh...」</t>
         </is>
       </c>
       <c r="C87" t="n">
@@ -1834,7 +1834,7 @@
       </c>
       <c r="B89" s="1" t="inlineStr">
         <is>
-          <t>A muffled sigh is saying that.</t>
+          <t>A muffled sigh seemed to say so.</t>
         </is>
       </c>
       <c r="C89" t="n">
@@ -1864,7 +1864,7 @@
       </c>
       <c r="B91" s="1" t="inlineStr">
         <is>
-          <t>「Fah… fuh… fuh, fuhhh… nnn…」</t>
+          <t>「fah… fuh… fuh, fuhhh… nnh…」</t>
         </is>
       </c>
       <c r="C91" t="n">
@@ -1879,7 +1879,7 @@
       </c>
       <c r="B92" s="1" t="inlineStr">
         <is>
-          <t>Breaths keep escaping from Rin-chan's mouth.</t>
+          <t>Sighs kept escaping from Rin-chan's lips.</t>
         </is>
       </c>
       <c r="C92" t="n">
@@ -1894,7 +1894,8 @@
       </c>
       <c r="B93" s="1" t="inlineStr">
         <is>
-          <t>She lifts Miru-chan's skirt and plays naughty pranks.</t>
+          <t>I usually lift Miru-chan's skirt and play lewd
+pranks.</t>
         </is>
       </c>
       <c r="C93" t="n">
@@ -1909,9 +1910,8 @@
       </c>
       <c r="B94" s="1" t="inlineStr">
         <is>
-          <t>When I have naughty thoughts, she’s the first to
-tease me about it, and she can be a bit precocious
-too.</t>
+          <t>Whenever I get lewd thoughts, Rin-chan's always the
+first to tease me — she's kind of precocious.</t>
         </is>
       </c>
       <c r="C94" t="n">
@@ -1926,8 +1926,8 @@
       </c>
       <c r="B95" s="1" t="inlineStr">
         <is>
-          <t>So I thought she was into sexual stuff, but I never
-expected her to be this bold...！</t>
+          <t>I thought Rin-chan was into sexual stuff, but I never
+expected her to be this bold...!</t>
         </is>
       </c>
       <c r="C95" t="n">
@@ -1942,7 +1942,7 @@
       </c>
       <c r="B96" s="1" t="inlineStr">
         <is>
-          <t>Rin-chan... you naughty girl！</t>
+          <t>Rin-chan... jeez, what a lewd girl!</t>
         </is>
       </c>
       <c r="C96" t="n">
@@ -1972,7 +1972,7 @@
       </c>
       <c r="B98" s="1" t="inlineStr">
         <is>
-          <t>「Ugh…！  Uh… ugh… phew… nn… nn…」</t>
+          <t>「Uuh…! Uh… uh… fuh… nnh… nnh…」</t>
         </is>
       </c>
       <c r="C98" t="n">
@@ -1987,7 +1987,7 @@
       </c>
       <c r="B99" s="1" t="inlineStr">
         <is>
-          <t>...Rin-chan's hip movement got a little bigger.</t>
+          <t>Rin-chan's hips moved a little more.</t>
         </is>
       </c>
       <c r="C99" t="n">
@@ -2002,7 +2002,7 @@
       </c>
       <c r="B100" s="1" t="inlineStr">
         <is>
-          <t>Along with that, my voice starts to go up.</t>
+          <t>Along with that, Rin-chan's voice grows higher.</t>
         </is>
       </c>
       <c r="C100" t="n">
@@ -2017,8 +2017,8 @@
       </c>
       <c r="B101" s="1" t="inlineStr">
         <is>
-          <t>From what I can see, she's merely pressing it so it
-digs into between-her-legs.</t>
+          <t>From what I can see, she's just pressing it so that
+it digs into the area between her legs.</t>
         </is>
       </c>
       <c r="C101" t="n">
@@ -2033,8 +2033,8 @@
       </c>
       <c r="B102" s="1" t="inlineStr">
         <is>
-          <t>But the bus's vibration must be nicely stimulating
-the soft flesh between her legs.</t>
+          <t>But the bus's vibrations were probably pleasantly
+stimulating the soft flesh between her legs.</t>
         </is>
       </c>
       <c r="C102" t="n">
@@ -2081,8 +2081,8 @@
       </c>
       <c r="B105" s="1" t="inlineStr">
         <is>
-          <t>...I replayed the time before I came here and the
-time after I arrived.</t>
+          <t>...I tried to recall the time before I came here and
+the time after I arrived.</t>
         </is>
       </c>
       <c r="C105" t="n">
@@ -2097,8 +2097,8 @@
       </c>
       <c r="B106" s="1" t="inlineStr">
         <is>
-          <t>Even if you subtract the hesitation time before
-Rin-chan started doing it, how many minutes has she
+          <t>Even if I subtract the hesitation time before
+Rin-chan engaged in the act, how many minutes has she
 actually been masturbating like this?</t>
         </is>
       </c>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="B107" s="1" t="inlineStr">
         <is>
-          <t>...So does that mean she's that absorbed in it？</t>
+          <t>So... does that mean Rin-chan's that into it?</t>
         </is>
       </c>
       <c r="C107" t="n">
@@ -2144,8 +2144,7 @@
       </c>
       <c r="B109" s="1" t="inlineStr">
         <is>
-          <t>「Nn, nmu...！ Ugh, nn... nnn... uh... un！ Uu...
-nnu...！」</t>
+          <t>「Nn… nmuu…！　Uuh… nn… nnh… u… un！　Uu… nnu…！」</t>
         </is>
       </c>
       <c r="C109" t="n">
@@ -2176,8 +2175,8 @@
       </c>
       <c r="B111" s="1" t="inlineStr">
         <is>
-          <t>She must have figured out that masturbating alone
-feels good.</t>
+          <t>Rin-chan must have figured out that masturbating
+alone feels good.</t>
         </is>
       </c>
       <c r="C111" t="n">
@@ -2192,8 +2191,8 @@
       </c>
       <c r="B112" s="1" t="inlineStr">
         <is>
-          <t>Even though she's small, she really is a girl after
-all….</t>
+          <t>Even though Rin-chan is so small, she's still a girl,
+isn't she...</t>
         </is>
       </c>
       <c r="C112" t="n">
@@ -2208,7 +2207,7 @@
       </c>
       <c r="B113" s="1" t="inlineStr">
         <is>
-          <t>I was moved all over again and pressed my groin.</t>
+          <t>I was moved again and clutched my crotch.</t>
         </is>
       </c>
       <c r="C113" t="n">
@@ -2223,8 +2222,8 @@
       </c>
       <c r="B114" s="1" t="inlineStr">
         <is>
-          <t>By the time my thoughts had gotten this far, I
-couldn't help but become aware of it myself.</t>
+          <t>Once my thoughts reached that point, I couldn't help
+becoming aware of my own arousal.</t>
         </is>
       </c>
       <c r="C114" t="n">
@@ -2254,8 +2253,8 @@
       </c>
       <c r="B116" s="1" t="inlineStr">
         <is>
-          <t>「Ugh, haa... ah, mm... fuu, fuu... uuh... nn,
-nnn...！」</t>
+          <t>「Uuh... haa... uh, mm... fuu, fuu... uuh... nn
+nnn!!!」</t>
         </is>
       </c>
       <c r="C116" t="n">
@@ -2286,8 +2285,8 @@
       </c>
       <c r="B118" s="1" t="inlineStr">
         <is>
-          <t>If we could masturbate together, how amazing would it
-feel？</t>
+          <t>Ah... I wonder how good it would feel if we could
+masturbate together?</t>
         </is>
       </c>
       <c r="C118" t="n">
@@ -2302,8 +2301,8 @@
       </c>
       <c r="B119" s="1" t="inlineStr">
         <is>
-          <t>I can’t help getting worked up, but I force myself to
-hold it back with reason.</t>
+          <t>I can't help getting aroused, but I force myself to
+suppress it.</t>
         </is>
       </c>
       <c r="C119" t="n">
@@ -2318,7 +2317,7 @@
       </c>
       <c r="B120" s="1" t="inlineStr">
         <is>
-          <t>If she found out, Rin-chan would definitely cry.</t>
+          <t>If it got found out, Rin-chan would definitely cry.</t>
         </is>
       </c>
       <c r="C120" t="n">
@@ -2333,8 +2332,7 @@
       </c>
       <c r="B121" s="1" t="inlineStr">
         <is>
-          <t>You must never do anything that would make a girl
-sad！</t>
+          <t>I must never do anything that would make a girl sad!</t>
         </is>
       </c>
       <c r="C121" t="n">
@@ -2364,7 +2362,7 @@
       </c>
       <c r="B123" s="1" t="inlineStr">
         <is>
-          <t>「U-uu...! Faah, ah...! Fuu, uuu...」</t>
+          <t>「Uuu...! Faa, ah...! Fuu, uuu...」</t>
         </is>
       </c>
       <c r="C123" t="n">
@@ -2394,7 +2392,7 @@
       </c>
       <c r="B125" s="1" t="inlineStr">
         <is>
-          <t>Wait, I still haven't been found out yet... right...？</t>
+          <t>Huh, I haven't been found out yet... right?</t>
         </is>
       </c>
       <c r="C125" t="n">
@@ -2409,8 +2407,8 @@
       </c>
       <c r="B126" s="1" t="inlineStr">
         <is>
-          <t>When I was panicking alone, Rin-chan pressed her lips
-together more tightly than before.</t>
+          <t>As I grew flustered on my own, Rin-chan pressed her
+lips together more tightly than before.</t>
         </is>
       </c>
       <c r="C126" t="n">
@@ -2440,7 +2438,7 @@
       </c>
       <c r="B128" s="1" t="inlineStr">
         <is>
-          <t>「…！　ck！　huh…nn！　nn！　n…u！　fuu…uuu！」</t>
+          <t>「…! Kk! Fuh… nn! Nn! Nn… u! Fuu… uuu!」</t>
         </is>
       </c>
       <c r="C128" t="n">
@@ -2471,7 +2469,7 @@
       </c>
       <c r="B130" s="1" t="inlineStr">
         <is>
-          <t>Huh, this is, um...？</t>
+          <t>Huh, is this... um...?</t>
         </is>
       </c>
       <c r="C130" t="n">
@@ -2486,7 +2484,7 @@
       </c>
       <c r="B131" s="1" t="inlineStr">
         <is>
-          <t>Seeing Rin-chan change, I give up trying to think.</t>
+          <t>Seeing the change in Rin-chan, I abandon all thought.</t>
         </is>
       </c>
       <c r="C131" t="n">
@@ -2547,7 +2545,7 @@
       </c>
       <c r="B135" s="1" t="inlineStr">
         <is>
-          <t>「fah... faaah... nngh, nnggh...？」</t>
+          <t>Fah... faaah... nn, nnn...?</t>
         </is>
       </c>
       <c r="C135" t="n">
@@ -2608,8 +2606,8 @@
       </c>
       <c r="B139" s="1" t="inlineStr">
         <is>
-          <t>Then, she gently let go of the shift lever between
-her legs...</t>
+          <t>Then, Rin-chan gently pulled her crotch away from the
+shift lever...</t>
         </is>
       </c>
       <c r="C139" t="n">
@@ -2624,8 +2622,7 @@
       </c>
       <c r="B140" s="1" t="inlineStr">
         <is>
-          <t>...Satisfied... no, has she come to terms with it, I
-wonder？</t>
+          <t>...Satisfied... no, maybe she's come to accept it?</t>
         </is>
       </c>
       <c r="C140" t="n">
@@ -2670,8 +2667,8 @@
       </c>
       <c r="B143" s="1" t="inlineStr">
         <is>
-          <t>Rin-chan straddled the shift lever and perched
-daintily on the driver's seat.</t>
+          <t>Rin-chan swung her leg over the gearshift and sat
+down lightly in the driver's seat.</t>
         </is>
       </c>
       <c r="C143" t="n">
@@ -2686,7 +2683,7 @@
       </c>
       <c r="B144" s="1" t="inlineStr">
         <is>
-          <t>She has kind of a spaced-out look on her face...</t>
+          <t>Rin-chan has a kind of spaced-out look on her face...</t>
         </is>
       </c>
       <c r="C144" t="n">
@@ -2701,8 +2698,8 @@
       </c>
       <c r="B145" s="1" t="inlineStr">
         <is>
-          <t>I didn't actually come, but did I get that close to
-it？</t>
+          <t>Even if Rin-chan didn't actually climax, maybe she
+ended up feeling something close to it?</t>
         </is>
       </c>
       <c r="C145" t="n">
@@ -2717,7 +2714,7 @@
       </c>
       <c r="B146" s="1" t="inlineStr">
         <is>
-          <t>I have to hide right now！</t>
+          <t>Ah, I have to hide while I still can!</t>
         </is>
       </c>
       <c r="C146" t="n">
@@ -2856,8 +2853,8 @@
       </c>
       <c r="B155" s="1" t="inlineStr">
         <is>
-          <t>But today it doesn't feel like a time I can ask
-anything.</t>
+          <t>But today doesn't feel like the kind of situation
+where I can ask anything.</t>
         </is>
       </c>
       <c r="C155" t="n">
